--- a/public/uploads/public/1F7020202049483420D8830538207720/employees/documents/ImportEmployee.xlsx
+++ b/public/uploads/public/1F7020202049483420D8830538207720/employees/documents/ImportEmployee.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64532F13-85FD-458A-BE4D-4E623CCAAE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94F02274-2067-481C-B5D2-1448222D0D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,26 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
-  <si>
-    <t>VOEUN VINDA</t>
-  </si>
-  <si>
-    <t>វឿន វិនដា</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>voeun.vinda@lccashexpress.com</t>
-  </si>
-  <si>
     <t>ខេត្តព្រះវិហារ</t>
   </si>
   <si>
-    <t>1921117-0993559-ស</t>
-  </si>
-  <si>
     <t>Married</t>
   </si>
   <si>
@@ -54,36 +42,12 @@
     <t>ភូមិ ស្ថាពរ ឃុំ ប៉ាលហាល ក្រុង ព្រះវិហារ  ខេត្ត ព្រះវិហារ</t>
   </si>
   <si>
-    <t>MIL SOKMENG</t>
-  </si>
-  <si>
-    <t>មិល សុខមេង</t>
-  </si>
-  <si>
-    <t>220198748</t>
-  </si>
-  <si>
-    <t>chem.oun@lccahexpress.com</t>
-  </si>
-  <si>
     <t>Single</t>
   </si>
   <si>
     <t xml:space="preserve"> ភូមិឡឥដ្ធ សង្កាត់កំពង់ប្រណាក់ ក្រុងព្រះវិហារ ខេត្តព្រះវិហារ</t>
   </si>
   <si>
-    <t>CHHEM OUN</t>
-  </si>
-  <si>
-    <t>ឆែម អូន</t>
-  </si>
-  <si>
-    <t>soeum.somen@lccashexress.com</t>
-  </si>
-  <si>
-    <t>1000922-2950544-ដ</t>
-  </si>
-  <si>
     <t>ភូមិ ស្វាយ ឃុំរណសិរ្ស ស្រុកសង្គមថ្មី ខេត្តព្រះវិហារ</t>
   </si>
   <si>
@@ -144,18 +108,6 @@
     <t>Khmer</t>
   </si>
   <si>
-    <t>Shift_A</t>
-  </si>
-  <si>
-    <t>0715444545</t>
-  </si>
-  <si>
-    <t>0972690910</t>
-  </si>
-  <si>
-    <t>085484469</t>
-  </si>
-  <si>
     <t>Admin Officer</t>
   </si>
   <si>
@@ -163,6 +115,75 @@
   </si>
   <si>
     <t>Salary (USD)</t>
+  </si>
+  <si>
+    <t>Half Day Morning</t>
+  </si>
+  <si>
+    <t>Half Day Afternoon</t>
+  </si>
+  <si>
+    <t>Heng Dara</t>
+  </si>
+  <si>
+    <t>Hin SokMeng</t>
+  </si>
+  <si>
+    <t>Khun Neary</t>
+  </si>
+  <si>
+    <t>ហេង តារា</t>
+  </si>
+  <si>
+    <t>ហីន សុខម៉េង</t>
+  </si>
+  <si>
+    <t>ឃុន នារី</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>90191990</t>
+  </si>
+  <si>
+    <t>90191991</t>
+  </si>
+  <si>
+    <t>90191992</t>
+  </si>
+  <si>
+    <t>heng.dara@gmail.com</t>
+  </si>
+  <si>
+    <t>hin.sokmeng@gmail.com</t>
+  </si>
+  <si>
+    <t>khun.neary@gmai.com</t>
+  </si>
+  <si>
+    <t>1921117-09959-ស</t>
+  </si>
+  <si>
+    <t>1000922-29544-ដ</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>In Probation</t>
+  </si>
+  <si>
+    <t>Full Day</t>
+  </si>
+  <si>
+    <t>012345678</t>
+  </si>
+  <si>
+    <t>012345679</t>
+  </si>
+  <si>
+    <t>012345680</t>
   </si>
 </sst>
 </file>
@@ -173,7 +194,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +235,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -247,11 +276,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -308,9 +338,13 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -649,153 +683,153 @@
     <col min="11" max="11" width="34.6640625" style="10" customWidth="1"/>
     <col min="12" max="12" width="21.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20" style="7" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" style="10"/>
-    <col min="15" max="15" width="13.33203125" style="15" customWidth="1"/>
-    <col min="16" max="16" width="19.6640625" style="18" customWidth="1"/>
-    <col min="17" max="17" width="14.21875" style="7" customWidth="1"/>
-    <col min="18" max="18" width="19.6640625" style="4" customWidth="1"/>
-    <col min="19" max="19" width="18" style="12" customWidth="1"/>
+    <col min="14" max="14" width="14.109375" style="10" customWidth="1"/>
+    <col min="15" max="15" width="15.33203125" style="15" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" style="18" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" style="7" customWidth="1"/>
+    <col min="18" max="18" width="24" style="4" customWidth="1"/>
+    <col min="19" max="19" width="20.109375" style="12" customWidth="1"/>
     <col min="20" max="20" width="57.109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="F2" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="K2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="13" t="s">
+      <c r="M2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="N2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="22.8" x14ac:dyDescent="0.8">
       <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="1">
-        <v>220085101</v>
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F3" s="14">
-        <v>46013</v>
+        <v>47474</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
       <c r="I3" s="14">
-        <v>33932</v>
+        <v>36854</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>3</v>
+        <v>50</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>42</v>
       </c>
       <c r="L3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="14">
+        <v>46252</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" s="11">
+        <v>250</v>
+      </c>
+      <c r="T3" s="8" t="s">
         <v>4</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="14">
-        <v>46251</v>
-      </c>
-      <c r="P3" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" s="11">
-        <v>1000</v>
-      </c>
-      <c r="T3" s="8" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="22.8" x14ac:dyDescent="0.8">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="F4" s="14">
-        <v>46420</v>
+        <v>47151</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
@@ -803,55 +837,55 @@
         <v>36714</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>12</v>
+        <v>51</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="9" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="O4" s="14">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="S4" s="11">
         <v>1000</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="22.8" x14ac:dyDescent="0.8">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="1">
-        <v>220173928</v>
+        <v>26</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F5" s="14">
-        <v>46240</v>
+        <v>47336</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
@@ -859,37 +893,37 @@
         <v>36770</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>17</v>
+        <v>52</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O5" s="14">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="Q5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S5" s="11">
+        <v>300</v>
+      </c>
+      <c r="T5" s="8" t="s">
         <v>7</v>
-      </c>
-      <c r="R5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="S5" s="11">
-        <v>1000</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -902,7 +936,12 @@
       <formula1>"Single, Married, Divorced"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K3" r:id="rId1" xr:uid="{945C5FA2-2865-4759-83ED-A6B0F57A58CD}"/>
+    <hyperlink ref="K4" r:id="rId2" xr:uid="{B27A6302-2CD9-44B8-BE2E-0CBA1EFCDCDF}"/>
+    <hyperlink ref="K5" r:id="rId3" xr:uid="{59D1BFAB-E458-4816-87E9-ADE1766D2D65}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>